--- a/Data/nodes.xlsx
+++ b/Data/nodes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1825,29 +1825,6 @@
         <v>8.5951427</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>180108</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Skjern</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Skjern, Ringkøbing-Skjern Kommune, Region Midtjylland, 6900, Danmark</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>55.9469339</v>
-      </c>
-      <c r="E65">
-        <v>8.490918600000001</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/nodes.xlsx
+++ b/Data/nodes.xlsx
@@ -1222,14 +1222,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Randers, Randers Kommune, Region Midtjylland, 8900, Danmark</t>
+          <t>Randers SV, Randers, Randers Kommune, Region Midtjylland, 8940, Danmark</t>
         </is>
       </c>
       <c r="D38">
-        <v>56.4617545</v>
+        <v>56.4355428</v>
       </c>
       <c r="E38">
-        <v>10.0371476</v>
+        <v>10.0425957</v>
       </c>
     </row>
     <row r="39">
